--- a/posts/inflation suisse/inflation_income_decomposition.xlsx
+++ b/posts/inflation suisse/inflation_income_decomposition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\celalguney\posts\inflation suisse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8C5CA1-E420-42CA-8B4A-4C596758C130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E794D537-261D-4C48-8EA6-7032FF508030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E69DC64F-2C82-4DC4-BC99-01B9323A830B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{E69DC64F-2C82-4DC4-BC99-01B9323A830B}"/>
   </bookViews>
   <sheets>
     <sheet name="data source" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="164">
   <si>
     <t>deflator</t>
   </si>
@@ -530,6 +530,9 @@
   </si>
   <si>
     <t xml:space="preserve">profit </t>
+  </si>
+  <si>
+    <t>inflation 2014-2017</t>
   </si>
 </sst>
 </file>
@@ -560,12 +563,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -580,12 +589,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,6 +948,9 @@
   <dimension ref="A1:W146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="25.81640625" customWidth="1"/>
+    <col min="7" max="7" width="23.90625" customWidth="1"/>
     <col min="8" max="8" width="27.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.453125" bestFit="1" customWidth="1"/>
@@ -1360,6 +1373,15 @@
         <f t="shared" si="10"/>
         <v>5.643002857354773E-2</v>
       </c>
+      <c r="T8" t="s">
+        <v>163</v>
+      </c>
+      <c r="U8" t="s">
+        <v>16</v>
+      </c>
+      <c r="V8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -1428,6 +1450,22 @@
         <f t="shared" si="10"/>
         <v>4.8082600375679352E-2</v>
       </c>
+      <c r="T9">
+        <f>E113/E98-1</f>
+        <v>-2.8052953027915883E-2</v>
+      </c>
+      <c r="U9">
+        <f>(H113-H98)/(E113-E98)*T9</f>
+        <v>5.9151593763411871E-2</v>
+      </c>
+      <c r="V9">
+        <f>(I113-I98)/(E113-E98)*T9</f>
+        <v>-8.7204546791335324E-2</v>
+      </c>
+      <c r="W9">
+        <f>V9+U9</f>
+        <v>-2.8052953027923454E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -3241,7 +3279,7 @@
         <v>-12.604016335558622</v>
       </c>
       <c r="M36">
-        <f t="shared" si="6"/>
+        <f>(I36-I32)/(E36-E32)</f>
         <v>13.604016335559217</v>
       </c>
       <c r="N36">
@@ -3257,11 +3295,11 @@
         <v>1.6431794498769504E-2</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="9"/>
+        <f>M36*K36</f>
         <v>-1.7735489611606012E-2</v>
       </c>
       <c r="R36">
-        <f t="shared" si="10"/>
+        <f>E36/E32-1</f>
         <v>-1.3036951128356788E-3</v>
       </c>
     </row>
@@ -10753,7 +10791,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584EA698-F8DF-41C3-9400-993E456395F5}">
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -11088,7 +11126,7 @@
       <c r="C24">
         <v>1.5178689288232441E-3</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="5">
         <v>-1.8273221842254328E-3</v>
       </c>
     </row>
@@ -11102,7 +11140,7 @@
       <c r="C25">
         <v>-5.4068095494052258E-4</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="5">
         <v>-3.9186506690388478E-3</v>
       </c>
     </row>
@@ -11116,7 +11154,7 @@
       <c r="C26">
         <v>-4.5660729183285148E-3</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="5">
         <v>-2.8495312987552035E-3</v>
       </c>
     </row>
@@ -11130,7 +11168,7 @@
       <c r="C27">
         <v>1.311675644169193E-2</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="5">
         <v>-8.8921061984328365E-3</v>
       </c>
     </row>
@@ -11144,7 +11182,7 @@
       <c r="C28">
         <v>-7.275993689769151E-4</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="5">
         <v>-3.3655584394668425E-3</v>
       </c>
     </row>
@@ -11158,7 +11196,7 @@
       <c r="C29">
         <v>-2.620083227800769E-2</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="5">
         <v>-3.8941770427726174E-3</v>
       </c>
     </row>
@@ -11172,7 +11210,7 @@
       <c r="C30">
         <v>1.7759505731218931E-3</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="5">
         <v>-1.4672292241131313E-3</v>
       </c>
     </row>
@@ -11186,7 +11224,7 @@
       <c r="C31">
         <v>-1.3447084833028245E-2</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="5">
         <v>-1.0043275297921817E-3</v>
       </c>
     </row>
@@ -11200,7 +11238,7 @@
       <c r="C32">
         <v>-1.7735489611606012E-2</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="5">
         <v>-1.3036951128356788E-3</v>
       </c>
     </row>
@@ -11214,7 +11252,7 @@
       <c r="C33">
         <v>7.1656129548350175E-3</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="5">
         <v>-3.7829859866962412E-3</v>
       </c>
     </row>
@@ -11228,7 +11266,7 @@
       <c r="C34">
         <v>2.1351065895006658E-2</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="5">
         <v>-2.9892511915011744E-3</v>
       </c>
     </row>
@@ -11242,7 +11280,7 @@
       <c r="C35">
         <v>-5.2368508777925064E-4</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="5">
         <v>-3.1668776268950483E-3</v>
       </c>
     </row>
@@ -11396,7 +11434,7 @@
       <c r="C46">
         <v>6.3307530834966388E-2</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="5">
         <v>-5.9393526062152535E-3</v>
       </c>
     </row>
@@ -11410,7 +11448,7 @@
       <c r="C47">
         <v>1.7992412316042816E-2</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="5">
         <v>-4.8549783517275458E-3</v>
       </c>
     </row>
@@ -11424,7 +11462,7 @@
       <c r="C48">
         <v>-5.7829752072674533E-3</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="5">
         <v>-6.3270539891481237E-3</v>
       </c>
     </row>
@@ -11438,7 +11476,7 @@
       <c r="C49">
         <v>-1.9636543621508996E-2</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="5">
         <v>-1.2378143792137752E-3</v>
       </c>
     </row>
@@ -12054,7 +12092,7 @@
       <c r="C93">
         <v>2.4497155640708984E-3</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="5">
         <v>-1.1197516150189823E-3</v>
       </c>
     </row>
@@ -12068,7 +12106,7 @@
       <c r="C94">
         <v>9.3856136068892694E-4</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="5">
         <v>-8.7389294025486119E-4</v>
       </c>
     </row>
@@ -12082,7 +12120,7 @@
       <c r="C95">
         <v>-7.058039166192619E-3</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="5">
         <v>-4.951066384948466E-3</v>
       </c>
     </row>
@@ -12096,7 +12134,7 @@
       <c r="C96">
         <v>-6.1110743413851053E-3</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="5">
         <v>-5.5189752464157582E-3</v>
       </c>
     </row>
@@ -12110,7 +12148,7 @@
       <c r="C97">
         <v>-7.6473599541946368E-3</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="5">
         <v>-1.2521885132219746E-2</v>
       </c>
     </row>
@@ -12124,7 +12162,7 @@
       <c r="C98">
         <v>-4.8216193957481036E-3</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="5">
         <v>-1.3074924504080765E-2</v>
       </c>
     </row>
@@ -12138,7 +12176,7 @@
       <c r="C99">
         <v>6.8436083711805162E-3</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="5">
         <v>-1.4650174625794099E-2</v>
       </c>
     </row>
@@ -12152,7 +12190,7 @@
       <c r="C100">
         <v>6.3315858707599882E-3</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="5">
         <v>-1.3694805764077667E-2</v>
       </c>
     </row>
@@ -12166,7 +12204,7 @@
       <c r="C101">
         <v>3.4340345119470431E-4</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="5">
         <v>-1.2423145704683058E-2</v>
       </c>
     </row>
@@ -12180,7 +12218,7 @@
       <c r="C102">
         <v>-1.3494338629834174E-2</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="5">
         <v>-1.2602191508990779E-2</v>
       </c>
     </row>
@@ -12194,7 +12232,7 @@
       <c r="C103">
         <v>-6.2268294036763499E-3</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="5">
         <v>-5.6802862374536467E-3</v>
       </c>
     </row>
@@ -12208,7 +12246,7 @@
       <c r="C104">
         <v>-3.4104277148532279E-4</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="5">
         <v>-4.3156731104214696E-3</v>
       </c>
     </row>
@@ -12222,7 +12260,7 @@
       <c r="C105">
         <v>2.8861847090420442E-3</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="5">
         <v>-2.0274642631799011E-3</v>
       </c>
     </row>
@@ -12236,7 +12274,7 @@
       <c r="C106">
         <v>-2.5627965635054983E-3</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="5">
         <v>-2.0686417037175664E-3</v>
       </c>
     </row>
@@ -12250,7 +12288,7 @@
       <c r="C107">
         <v>5.1218179339910736E-3</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="5">
         <v>-1.0340613347591954E-2</v>
       </c>
     </row>
@@ -12264,7 +12302,7 @@
       <c r="C108">
         <v>1.727669722537666E-3</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="5">
         <v>-3.2385987818760453E-3</v>
       </c>
     </row>
@@ -12324,7 +12362,7 @@
         <v>8.5236354873770015E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>131</v>
       </c>
@@ -12338,12 +12376,12 @@
         <v>6.6737138207648705E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>132</v>
       </c>
       <c r="B114">
-        <v>-8.4750611928768123E-4</v>
+        <v>-8.4750611928768101E-4</v>
       </c>
       <c r="C114">
         <v>9.7165268614111781E-3</v>
@@ -12352,7 +12390,7 @@
         <v>8.8690207421189271E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>133</v>
       </c>
@@ -12362,11 +12400,15 @@
       <c r="C115">
         <v>1.3804105500748204E-2</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="5">
         <v>-1.4063444791946322E-3</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E115">
+        <f>SUM(B115:B120)</f>
+        <v>-9.0963560727712209E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>134</v>
       </c>
@@ -12376,11 +12418,11 @@
       <c r="C116">
         <v>8.0031673526245566E-3</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="5">
         <v>-4.3913277888241176E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>135</v>
       </c>
@@ -12390,11 +12432,11 @@
       <c r="C117">
         <v>8.5560423854887067E-3</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="5">
         <v>-6.3152036439335646E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>136</v>
       </c>
@@ -12404,11 +12446,11 @@
       <c r="C118">
         <v>8.4608496920471864E-3</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="5">
         <v>-1.069556037987629E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>137</v>
       </c>
@@ -12418,11 +12460,11 @@
       <c r="C119">
         <v>5.2078695762059262E-3</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="5">
         <v>-1.1646946445152628E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>138</v>
       </c>
@@ -12432,11 +12474,11 @@
       <c r="C120">
         <v>5.7476850997314286E-3</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="5">
         <v>-6.7284583838753687E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>139</v>
       </c>
@@ -12446,11 +12488,11 @@
       <c r="C121">
         <v>-4.462857690991218E-3</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="5">
         <v>-1.7187191306018423E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>140</v>
       </c>
@@ -12464,7 +12506,7 @@
         <v>6.8993273189352777E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>141</v>
       </c>
@@ -12478,7 +12520,7 @@
         <v>2.0532500890611427E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>142</v>
       </c>
@@ -12492,7 +12534,7 @@
         <v>2.1840655250882302E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>143</v>
       </c>
@@ -12506,7 +12548,7 @@
         <v>2.745385141966139E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>144</v>
       </c>
@@ -12520,7 +12562,7 @@
         <v>3.4698549553505487E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>145</v>
       </c>
@@ -12534,7 +12576,7 @@
         <v>3.0582210678776311E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>146</v>
       </c>
